--- a/human_resources_forms/032_hr_audit_form--human_resources_forms.xlsx
+++ b/human_resources_forms/032_hr_audit_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'hr',_'value':_'hr'}</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'HR', 'value': 'HR'}</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'finance',_'value':_'finance'}</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Finance', 'value': 'Finance'}</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'operations',_'value':_'operations'}</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Operations', 'value': 'Operations'}</t>
+          <t>Operations</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'manager',_'value':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Manager', 'value': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'non-manager',_'value':_'non-manager'}</t>
+          <t>non-manager</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Non-Manager', 'value': 'Non-Manager'}</t>
+          <t>Non-Manager</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'john_smith',_'value':_'john_smith'}</t>
+          <t>john_smith</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'John Smith', 'value': 'John Smith'}</t>
+          <t>John Smith</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'jane_doe',_'value':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Jane Doe', 'value': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'pass',_'value':_'pass'}</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Pass', 'value': 'Pass'}</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fail',_'value':_'fail'}</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fail', 'value': 'Fail'}</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'health',_'value':_'health'}</t>
+          <t>health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Health', 'value': 'Health'}</t>
+          <t>Health</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'dental',_'value':_'dental'}</t>
+          <t>dental</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Dental', 'value': 'Dental'}</t>
+          <t>Dental</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'vision',_'value':_'vision'}</t>
+          <t>vision</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Vision', 'value': 'Vision'}</t>
+          <t>Vision</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'401(k)',_'value':_'401(k)'}</t>
+          <t>401(k)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '401(k)', 'value': '401(k)'}</t>
+          <t>401(k)</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'life',_'value':_'life'}</t>
+          <t>life</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Life', 'value': 'Life'}</t>
+          <t>Life</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'mandatory',_'value':_'mandatory'}</t>
+          <t>mandatory</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Mandatory', 'value': 'Mandatory'}</t>
+          <t>Mandatory</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'optional',_'value':_'optional'}</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Optional', 'value': 'Optional'}</t>
+          <t>Optional</t>
         </is>
       </c>
     </row>
